--- a/docs/techs.xlsx
+++ b/docs/techs.xlsx
@@ -441,9 +441,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -465,9 +463,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
@@ -583,9 +579,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
@@ -821,7 +815,6 @@
           <t>{"rows": 1}</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -845,7 +838,6 @@
       <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>仓库往下长，放得下更多带回来的东西；仓库里的东西原地不动。</t>
@@ -856,8 +848,6 @@
           <t>warehouse_rows</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -881,7 +871,6 @@
       <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>体力上限更高，在图上走得更远。</t>
@@ -1117,7 +1106,6 @@
       <c r="E10" t="n">
         <v>0</v>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>每个搜索点能多搜几次。</t>
@@ -1247,7 +1235,6 @@
       <c r="C2" t="n">
         <v>400</v>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>{"amount": 50}</t>
@@ -1266,7 +1253,6 @@
       <c r="C3" t="n">
         <v>800</v>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>{"amount": 100}</t>
@@ -1285,7 +1271,11 @@
       <c r="C4" t="n">
         <v>1200</v>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>tanned_leather: 2；linen_bolt: 1</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>{"amount": 150}</t>
@@ -1304,8 +1294,6 @@
       <c r="C5" t="n">
         <v>300</v>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1321,10 +1309,9 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>steel_ingot: 2；rivet_box: 1</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>nail_keg: 1；steel_ingot: 1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1338,8 +1325,6 @@
       <c r="C7" t="n">
         <v>100</v>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1353,8 +1338,6 @@
       <c r="C8" t="n">
         <v>200</v>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1368,8 +1351,6 @@
       <c r="C9" t="n">
         <v>400</v>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1388,7 +1369,6 @@
           <t>steel_ingot: 2</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1404,10 +1384,9 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>hardwood_plank: 2；steel_ingot: 3</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>hardwood_plank: 2；steel_ingot: 3；nail_keg: 1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1426,7 +1405,6 @@
           <t>hardwood_plank: 3；rivet_box: 2；steel_ingot: 4</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1440,8 +1418,6 @@
       <c r="C13" t="n">
         <v>200</v>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1455,7 +1431,6 @@
       <c r="C14" t="n">
         <v>500</v>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>{"amount": 2}</t>
@@ -1474,7 +1449,6 @@
       <c r="C15" t="n">
         <v>900</v>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>{"amount": 3}</t>
@@ -1498,7 +1472,6 @@
           <t>hardwood_plank: 2；steel_ingot: 2</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1512,7 +1485,6 @@
       <c r="C17" t="n">
         <v>300</v>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>{"amount": 5.0}</t>
@@ -1531,7 +1503,6 @@
       <c r="C18" t="n">
         <v>700</v>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>{"amount": 10.0}</t>
@@ -1550,7 +1521,11 @@
       <c r="C19" t="n">
         <v>1200</v>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>copper_ingot: 2</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>{"amount": 15.0}</t>
@@ -1569,8 +1544,6 @@
       <c r="C20" t="n">
         <v>400</v>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1584,7 +1557,6 @@
       <c r="C21" t="n">
         <v>800</v>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>{"amount": 2}</t>
@@ -1649,8 +1621,6 @@
       <c r="C24" t="n">
         <v>250</v>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1664,7 +1634,6 @@
       <c r="C25" t="n">
         <v>700</v>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>{"amount": 2}</t>
@@ -1683,7 +1652,6 @@
       <c r="C26" t="n">
         <v>500</v>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>{"factor": 0.95}</t>
@@ -1702,8 +1670,11 @@
       <c r="C27" t="n">
         <v>1000</v>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>silver_ingot: 1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/techs.xlsx
+++ b/docs/techs.xlsx
@@ -441,7 +441,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -463,7 +462,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
@@ -579,7 +577,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
@@ -658,7 +655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1039,33 +1036,33 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>scouting</t>
+          <t>hauling</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>侦察</t>
+          <t>扛重</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Scouting</t>
+          <t>Hauling</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
         <v>2</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>luck、bargain</t>
+          <t>endurance</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>隐形的猎手走近到一定距离就看得见。</t>
+          <t>背得更多再开始吃力。</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1075,29 +1072,29 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{"effect": "scout_range"}</t>
+          <t>{"effect": "carry_capacity_bonus"}</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>侦察距离 {scout_range_range}</t>
+          <t>负重上限 {carry_capacity_bonus_amount|signed}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>thorough_search</t>
+          <t>scouting</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>细搜</t>
+          <t>侦察</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thorough Search</t>
+          <t>Scouting</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1106,9 +1103,14 @@
       <c r="E10" t="n">
         <v>0</v>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>luck、bargain</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>每个搜索点能多搜几次。</t>
+          <t>隐形的猎手走近到一定距离就看得见。</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1118,58 +1120,101 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{"effect": "extra_searches"}</t>
+          <t>{"effect": "scout_range"}</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>每个搜索点多搜 {extra_searches_amount} 次</t>
+          <t>侦察距离 {scout_range_range}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bargain</t>
+          <t>thorough_search</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>讨价</t>
+          <t>细搜</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Haggling</t>
+          <t>Thorough Search</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
       <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>每个搜索点能多搜几次。</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>tech_run_buff</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>{"effect": "extra_searches"}</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>每个搜索点多搜 {extra_searches_amount} 次</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>bargain</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>讨价</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Haggling</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
         <v>1</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>thorough_search</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>商店的东西更便宜。</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>tech_run_buff</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>{"effect": "shop_price_mult"}</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>商店售价 ×{shop_price_mult_factor}</t>
         </is>
@@ -1186,7 +1231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1535,142 +1580,206 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>luck</t>
+          <t>hauling</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>400</v>
+        <v>300</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>{"amount": 6}</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>luck</t>
+          <t>hauling</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>800</v>
+        <v>700</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>beast_hide: 1；rope_coil: 2</t>
+        </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>{"amount": 2}</t>
+          <t>{"amount": 12}</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>luck</t>
+          <t>hauling</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>hardwood_plank: 2；rivet_box: 2</t>
+          <t>tanned_leather: 2；hardwood_plank: 1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>{"amount": 3}</t>
+          <t>{"amount": 20}</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>scouting</t>
+          <t>luck</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>steel_ingot: 3；hardwood_plank: 2；rivet_box: 2</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>{"range": 3.0}</t>
-        </is>
+        <v>400</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>thorough_search</t>
+          <t>luck</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>250</v>
+        <v>800</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>{"amount": 2}</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>thorough_search</t>
+          <t>luck</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>700</v>
+        <v>1300</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>hardwood_plank: 2；rivet_box: 2</t>
+        </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>{"amount": 2}</t>
+          <t>{"amount": 3}</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bargain</t>
+          <t>scouting</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>500</v>
+        <v>1500</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>steel_ingot: 3；hardwood_plank: 2；rivet_box: 2</t>
+        </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>{"factor": 0.95}</t>
+          <t>{"range": 3.0}</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>thorough_search</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>thorough_search</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" t="n">
+        <v>700</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>{"amount": 2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>bargain</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>500</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>{"factor": 0.95}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>bargain</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
         <v>2</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C30" t="n">
         <v>1000</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>silver_ingot: 1</t>
         </is>

--- a/docs/techs.xlsx
+++ b/docs/techs.xlsx
@@ -751,7 +751,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>出发时多带一笔钱。</t>
+          <t>出发时多带一笔钱：按角色自己的开局钱加百分比。</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>开局钱 {starting_funds_bonus_amount|signed}</t>
+          <t>开局钱 {starting_funds_bonus_percent|signed}%</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>体力上限更高，在图上走得更远。</t>
+          <t>体力上限更高，在图上走得更远：按角色自己的体力上限加百分比。</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>体力上限 {vitality_max_bonus_amount|signed}</t>
+          <t>体力上限 {vitality_max_bonus_percent|signed}%</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>输给节点敌人的头一次不扣体力。</t>
+          <t>打输了少扣体力，最少还是扣一点。</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{"effect": "free_losses"}</t>
+          <t>{"effect": "loss_discount"}</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>前 {free_losses_amount} 次输给节点敌人不扣体力</t>
+          <t>打输了少扣 {loss_discount_amount} 点体力（最少扣一点）</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>开局生命上限更高。</t>
+          <t>开局生命上限更高：按角色自己的生命加百分比。</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>开局生命 {stat_bonus_amount|signed}</t>
+          <t>开局生命 {stat_bonus_amount|signed}%</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>背得更多再开始吃力。</t>
+          <t>背得更多再开始吃力：按角色自己的负重上限加百分比。</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>负重上限 {carry_capacity_bonus_amount|signed}</t>
+          <t>负重上限 {carry_capacity_bonus_percent|signed}%</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>{"amount": 50}</t>
+          <t>{"percent": 25, "amount": 0}</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>{"amount": 100}</t>
+          <t>{"percent": 50, "amount": 0}</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>{"amount": 150}</t>
+          <t>{"percent": 100, "amount": 0}</t>
         </is>
       </c>
     </row>
@@ -1463,6 +1463,11 @@
       <c r="C13" t="n">
         <v>200</v>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>{"percent": 20, "amount": 0}</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1478,7 +1483,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>{"amount": 2}</t>
+          <t>{"percent": 40, "amount": 0}</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1501,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>{"amount": 3}</t>
+          <t>{"percent": 60, "amount": 0}</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1537,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>{"amount": 5.0}</t>
+          <t>{"mode": "MULT", "amount": 10}</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1555,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>{"amount": 10.0}</t>
+          <t>{"mode": "MULT", "amount": 20}</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1578,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>{"amount": 15.0}</t>
+          <t>{"mode": "MULT", "amount": 30}</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1596,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>{"amount": 6}</t>
+          <t>{"percent": 15, "amount": 0}</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1619,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>{"amount": 12}</t>
+          <t>{"percent": 30, "amount": 0}</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1642,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>{"amount": 20}</t>
+          <t>{"percent": 50, "amount": 0}</t>
         </is>
       </c>
     </row>

--- a/docs/techs.xlsx
+++ b/docs/techs.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RunRegistry.TECH_EFFECTS 里的类型：warehouse_rows / tech_safe_size / tech_run_buff</t>
+          <t>RunRegistry.TECH_EFFECTS 里的类型：warehouse_pages / tech_safe_size / tech_run_buff / tech_belt_grant</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>仓库往下长，放得下更多带回来的东西；仓库里的东西原地不动。</t>
+          <t>仓库多一页，放得下更多带回来的东西；各页独立，左边的页签切换。</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>warehouse_rows</t>
+          <t>warehouse_pages</t>
         </is>
       </c>
     </row>

--- a/docs/techs.xlsx
+++ b/docs/techs.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -441,6 +441,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -462,6 +463,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
@@ -544,101 +546,114 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>效果构件</t>
+          <t>英文说明</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RunRegistry.TECH_EFFECTS 里的类型：warehouse_pages / tech_safe_size / tech_run_buff / tech_belt_grant</t>
+          <t>descriptions.en，可空；不写数字（TextLint）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>构件参数（JSON）</t>
+          <t>效果构件</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>构件自己的字段：tech_safe_size 填 {"cols": 0, "rows": 1}；tech_run_buff 填 {"effect": "&lt;RUN_EFFECTS 里的类型&gt;"}，每级的 run_buff 由工具生成（id = tech_&lt;id&gt;_&lt;级&gt;，scope META）</t>
+          <t>RunRegistry.TECH_EFFECTS 里的类型：warehouse_pages / tech_safe_size / tech_run_buff / tech_belt_grant</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>构件参数（JSON）</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>构件自己的字段：tech_safe_size 填 {"cols": 0, "rows": 1}；tech_run_buff 填 {"effect": "&lt;RUN_EFFECTS 里的类型&gt;"}，每级的 run_buff 由工具生成（id = tech_&lt;id&gt;_&lt;级&gt;，scope META）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>每级说明模板</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>只 tech_run_buff 用：生成的 run_buff 的 description，占位符照 docs/text-placeholders.md，不写数字</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>等级表的列</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>科技 id</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>对应节点表的 id；一个科技有几行就有几级，级号从 1 起连续</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>级</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>升到第几级</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>钱</t>
+          <t>级</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>这一级要的钱（TechTier.funds），整数</t>
+          <t>升到第几级</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>材料</t>
+          <t>钱</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>道具 id: 数量，多个用「；」分开，如 steel_ingot: 2；rivet_box: 1。空 = 不要材料（TechTier.items）</t>
+          <t>这一级要的钱（TechTier.funds），整数</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>材料</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>道具 id: 数量，多个用「；」分开，如 steel_ingot: 2；rivet_box: 1。空 = 不要材料（TechTier.items）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>效果参数（JSON）</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>只 tech_run_buff 用：这一级 run_buff 效果的参数，如 {"amount": 3}；空 = 全用默认值。别的构件这格留空（它们按级数自己算）</t>
         </is>
@@ -655,7 +670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -706,17 +721,22 @@
           <t>说明</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>英文说明</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>效果构件</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>构件参数（JSON）</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>每级说明模板</t>
         </is>
@@ -756,15 +776,20 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>Set out with extra money: a percentage of the character's own starting money.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>tech_run_buff</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>{"effect": "starting_funds_bonus"}</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>开局钱 {starting_funds_bonus_percent|signed}%</t>
         </is>
@@ -804,10 +829,15 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>The safe in a run gets more cells, so more is kept even if you fail to extract.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>tech_safe_size</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>{"rows": 1}</t>
         </is>
@@ -842,6 +872,11 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>One more Warehouse page for what you bring back; each page is separate, switch with the tabs on the left.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>warehouse_pages</t>
         </is>
       </c>
@@ -875,15 +910,20 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>Higher max Vitality, so you travel further on the map: a percentage of the character's own max Vitality.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>tech_run_buff</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>{"effect": "vitality_max_bonus"}</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>体力上限 {vitality_max_bonus_percent|signed}%</t>
         </is>
@@ -923,15 +963,20 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>Lose less Vitality when you lose a battle, but always at least one point.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>tech_run_buff</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>{"effect": "loss_discount"}</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>打输了少扣 {loss_discount_amount} 点体力（最少扣一点）</t>
         </is>
@@ -971,15 +1016,20 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>Higher max Health at the start: a percentage of the character's own Health.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>tech_run_buff</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>{"effect": "stat_bonus"}</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>开局生命 {stat_bonus_amount|signed}%</t>
         </is>
@@ -1019,15 +1069,20 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>Enemies drop their things more often.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>tech_run_buff</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>{"effect": "luck_bonus"}</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>幸运 {luck_bonus_amount|signed}：敌人的东西更容易掉</t>
         </is>
@@ -1067,15 +1122,20 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>Carry more before it gets heavy: a percentage of the character's own Load limit.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>tech_run_buff</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>{"effect": "carry_capacity_bonus"}</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>负重上限 {carry_capacity_bonus_percent|signed}%</t>
         </is>
@@ -1115,15 +1175,20 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>Hidden hunters become visible once they come close enough.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>tech_run_buff</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>{"effect": "scout_range"}</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>侦察距离 {scout_range_range}</t>
         </is>
@@ -1158,15 +1223,20 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>Search each search spot a few more times.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>tech_run_buff</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>{"effect": "extra_searches"}</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>每个搜索点多搜 {extra_searches_amount} 次</t>
         </is>
@@ -1206,15 +1276,20 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>Shop prices are lower.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>tech_run_buff</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>{"effect": "shop_price_mult"}</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>商店售价 ×{shop_price_mult_factor}</t>
         </is>

--- a/docs/techs.xlsx
+++ b/docs/techs.xlsx
@@ -441,7 +441,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -463,7 +462,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
@@ -591,7 +589,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -953,7 +950,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>endurance</t>
+          <t>sinew</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1165,7 +1162,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>luck、bargain</t>
+          <t>bargain</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1266,7 +1263,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>thorough_search</t>
+          <t>luck</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">

--- a/docs/techs.xlsx
+++ b/docs/techs.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="节点" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="等级" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="节点" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -768,12 +768,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>出发时多带一笔钱：按角色自己的开局钱加百分比。</t>
+          <t>死里逃生：战败时保住身上一部分钱，级数越高留得越多。</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Set out with extra money: a percentage of the character's own starting money.</t>
+          <t>Keep part of the coins you're carrying if you die; higher levels keep more.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>{"effect": "starting_funds_bonus"}</t>
+          <t>{"effect": "keep_on_death"}</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>开局钱 {starting_funds_bonus_percent|signed}%</t>
+          <t>战败时保住身上一部分钱</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>{"percent": 25, "amount": 0}</t>
+          <t>{"percent": 20}</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>{"percent": 50, "amount": 0}</t>
+          <t>{"percent": 30}</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>{"percent": 100, "amount": 0}</t>
+          <t>{"percent": 50}</t>
         </is>
       </c>
     </row>

--- a/docs/techs.xlsx
+++ b/docs/techs.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="节点" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="说明" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="节点" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="等级" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1292,6 +1292,102 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>集市</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>bargain</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>基地里开一间集市，卖药、食物、弹药与低档素材；每一局回来换一次货。级数越高，货格越多、素材档次越高。</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Opens a market at your base selling remedies, food, ammo and low-grade materials; new stock after every run. Higher levels mean more slots and better materials.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>tech_facility</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>{"facility": "market"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>smithy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>铁匠铺</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Smithy</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>warehouse</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>基地里开一间铁匠铺，按配方用仓库里的素材加钱打造武器、防具。级数越高，会打的档次越高。</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Opens a smithy at your base that forges weapons and armour from Warehouse materials plus coins, by recipe. Higher levels unlock better recipes.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>tech_facility</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>{"facility": "smithy"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1303,7 +1399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1862,6 +1958,104 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>hardwood_plank: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>steel_ingot: 2；nail_keg: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>smithy</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>smithy</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>steel_ingot: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>smithy</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>hardwood_plank: 2；rivet_box: 2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/techs.xlsx
+++ b/docs/techs.xlsx
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>2</v>
@@ -1357,14 +1357,14 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>warehouse</t>
+          <t>pack</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">

--- a/docs/techs.xlsx
+++ b/docs/techs.xlsx
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1388,6 +1388,102 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>mithril_smelting</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>秘银冶炼</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Mithril Smelting</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>smithy</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>学会炼秘银：银锭加钱炼成秘银锭，再用它打更好的刀剑。</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Learn to smelt mithril: turn Silver Ingots and coins into Mithril Ingots, then forge better blades with them.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>tech_recipes</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>{"tech": "mithril_smelting"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>staffcraft</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>法杖工艺</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Staffcraft</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>smithy</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>学会做法杖：级数越高，做得出的杖越好。</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Learn to make staves: higher levels make better staves.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>tech_recipes</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>{"tech": "staffcraft"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1399,7 +1495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2056,6 +2152,78 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>mithril_smelting</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>silver_ingot: 2；crystal_shards: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>staffcraft</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>600</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>crystal_shards: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>staffcraft</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>fire_crystal_low: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>staffcraft</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>silver_ingot: 2；fire_crystal: 1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/techs.xlsx
+++ b/docs/techs.xlsx
@@ -1300,12 +1300,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>集市</t>
+          <t>高级货物</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Market</t>
+          <t>Finer Goods</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1321,12 +1321,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>基地里开一间集市，卖药、食物、弹药与低档素材；每一局回来换一次货。级数越高，货格越多、素材档次越高。</t>
+          <t>集市进更好的货：级数越高，货格越多、素材档次越高。</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Opens a market at your base selling remedies, food, ammo and low-grade materials; new stock after every run. Higher levels mean more slots and better materials.</t>
+          <t>The market stocks finer goods: higher levels mean more slots and better materials.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>铁匠铺</t>
+          <t>高级配方</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Smithy</t>
+          <t>Advanced Recipes</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>基地里开一间铁匠铺，按配方用仓库里的素材加钱打造武器、防具。级数越高，会打的档次越高。</t>
+          <t>铁匠铺接更难的活：级数越高，打得出的配方档次越高。</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Opens a smithy at your base that forges weapons and armour from Warehouse materials plus coins, by recipe. Higher levels unlock better recipes.</t>
+          <t>The smithy takes on harder work: higher levels unlock better recipes.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1495,7 +1495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2064,7 +2064,12 @@
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>600</v>
+        <v>1200</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>hardwood_plank: 2</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -2077,29 +2082,29 @@
         <v>2</v>
       </c>
       <c r="C32" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>hardwood_plank: 2</t>
+          <t>steel_ingot: 2；nail_keg: 1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>market</t>
+          <t>smithy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>steel_ingot: 2；nail_keg: 1</t>
+          <t>steel_ingot: 2</t>
         </is>
       </c>
     </row>
@@ -2110,63 +2115,68 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34" t="n">
-        <v>500</v>
+        <v>1800</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>hardwood_plank: 2；rivet_box: 2</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>smithy</t>
+          <t>mithril_smelting</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>steel_ingot: 2</t>
+          <t>silver_ingot: 2；crystal_shards: 3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>smithy</t>
+          <t>staffcraft</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>1800</v>
+        <v>600</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>hardwood_plank: 2；rivet_box: 2</t>
+          <t>crystal_shards: 3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>mithril_smelting</t>
+          <t>staffcraft</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" t="n">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>silver_ingot: 2；crystal_shards: 3</t>
+          <t>fire_crystal_low: 1</t>
         </is>
       </c>
     </row>
@@ -2177,48 +2187,12 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C38" t="n">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="D38" t="inlineStr">
-        <is>
-          <t>crystal_shards: 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>staffcraft</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>2</v>
-      </c>
-      <c r="C39" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>fire_crystal_low: 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>staffcraft</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>3</v>
-      </c>
-      <c r="C40" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D40" t="inlineStr">
         <is>
           <t>silver_ingot: 2；fire_crystal: 1</t>
         </is>

--- a/docs/techs.xlsx
+++ b/docs/techs.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="节点" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="等级" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="节点" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>集市进更好的货：级数越高，货格越多、素材档次越高。</t>
+          <t>集市进更好的货：固定摊位进绿色、蓝色货，散货摊货位更多。</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>The market stocks finer goods: higher levels mean more slots and better materials.</t>
+          <t>The market stocks finer goods: fixed stalls carry green and blue wares, and the Bazaar gets more slots.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
